--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/67.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/67.xlsx
@@ -426,13 +426,13 @@
         <v>-19.17736158163919</v>
       </c>
       <c r="E2">
-        <v>-10.19919879032106</v>
+        <v>-7.211818829149022</v>
       </c>
       <c r="F2">
-        <v>-0.9893483292700553</v>
+        <v>-0.9747143907321992</v>
       </c>
       <c r="G2">
-        <v>-12.5573936524093</v>
+        <v>-9.345379880023438</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-18.93364823234692</v>
       </c>
       <c r="E3">
-        <v>-9.358324565732786</v>
+        <v>-7.476272654248955</v>
       </c>
       <c r="F3">
-        <v>-1.205385719552764</v>
+        <v>-0.6761152781472698</v>
       </c>
       <c r="G3">
-        <v>-12.04300108651734</v>
+        <v>-9.97454243867085</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-18.55056447281122</v>
       </c>
       <c r="E4">
-        <v>-10.66883777270854</v>
+        <v>-8.506183497813424</v>
       </c>
       <c r="F4">
-        <v>-0.9491774804386961</v>
+        <v>-0.8708205510730852</v>
       </c>
       <c r="G4">
-        <v>-11.91776976985779</v>
+        <v>-9.312896807192111</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-18.04998803956104</v>
       </c>
       <c r="E5">
-        <v>-12.63254259902468</v>
+        <v>-8.476875214035783</v>
       </c>
       <c r="F5">
-        <v>-0.6444757851973427</v>
+        <v>-1.040794915188321</v>
       </c>
       <c r="G5">
-        <v>-10.97286061985685</v>
+        <v>-9.053320242003396</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-17.45350034174493</v>
       </c>
       <c r="E6">
-        <v>-13.39699882473352</v>
+        <v>-10.4473591659414</v>
       </c>
       <c r="F6">
-        <v>-0.6758659395590272</v>
+        <v>-0.8311243567635301</v>
       </c>
       <c r="G6">
-        <v>-10.84556021223526</v>
+        <v>-8.298045761582989</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-16.79456293773191</v>
       </c>
       <c r="E7">
-        <v>-12.54017078621622</v>
+        <v>-11.04207007194672</v>
       </c>
       <c r="F7">
-        <v>-0.8911188659112843</v>
+        <v>-0.6955794270108498</v>
       </c>
       <c r="G7">
-        <v>-10.5160285092562</v>
+        <v>-8.540606122699849</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-16.12556380222479</v>
       </c>
       <c r="E8">
-        <v>-14.37181172504666</v>
+        <v>-10.7815786616035</v>
       </c>
       <c r="F8">
-        <v>-0.9413295276645736</v>
+        <v>-0.3063983389297945</v>
       </c>
       <c r="G8">
-        <v>-10.14115557457129</v>
+        <v>-8.843474691905612</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-15.49396074301633</v>
       </c>
       <c r="E9">
-        <v>-13.0716868374445</v>
+        <v>-12.31905445736969</v>
       </c>
       <c r="F9">
-        <v>-0.5308229491658477</v>
+        <v>-0.6674994287907522</v>
       </c>
       <c r="G9">
-        <v>-10.04209080985414</v>
+        <v>-7.067800691552265</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-14.96109906252081</v>
       </c>
       <c r="E10">
-        <v>-15.21302558518552</v>
+        <v>-12.63041421624107</v>
       </c>
       <c r="F10">
-        <v>-0.3741405683959325</v>
+        <v>-0.5023710139818931</v>
       </c>
       <c r="G10">
-        <v>-9.241835947191655</v>
+        <v>-7.281287841743247</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-14.5663522995386</v>
       </c>
       <c r="E11">
-        <v>-15.02899745846181</v>
+        <v>-12.10098579153032</v>
       </c>
       <c r="F11">
-        <v>-0.4294796527399534</v>
+        <v>-0.6415914099007949</v>
       </c>
       <c r="G11">
-        <v>-9.745796984089369</v>
+        <v>-6.760658208055303</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-14.35318956888329</v>
       </c>
       <c r="E12">
-        <v>-14.99300967552285</v>
+        <v>-13.23467567392857</v>
       </c>
       <c r="F12">
-        <v>-0.1559858710316687</v>
+        <v>-0.597465106721068</v>
       </c>
       <c r="G12">
-        <v>-8.76317740985059</v>
+        <v>-5.9920985083858</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-14.3301848651614</v>
       </c>
       <c r="E13">
-        <v>-16.41505014035951</v>
+        <v>-13.55512408013335</v>
       </c>
       <c r="F13">
-        <v>0.06281081106976476</v>
+        <v>-0.7911523161088427</v>
       </c>
       <c r="G13">
-        <v>-9.277348169191416</v>
+        <v>-5.967726272125685</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-14.50538395596651</v>
       </c>
       <c r="E14">
-        <v>-17.17107434746607</v>
+        <v>-15.21441582670587</v>
       </c>
       <c r="F14">
-        <v>-0.01837250787419799</v>
+        <v>-0.04430951962325331</v>
       </c>
       <c r="G14">
-        <v>-8.459030970066667</v>
+        <v>-5.161800444954429</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-14.85377115070506</v>
       </c>
       <c r="E15">
-        <v>-18.56992902538346</v>
+        <v>-15.33620913514216</v>
       </c>
       <c r="F15">
-        <v>0.4054268823372515</v>
+        <v>0.4816424819666256</v>
       </c>
       <c r="G15">
-        <v>-8.281850572804874</v>
+        <v>-6.099204588217841</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-15.34813188413086</v>
       </c>
       <c r="E16">
-        <v>-19.31669250314433</v>
+        <v>-16.76275543161646</v>
       </c>
       <c r="F16">
-        <v>0.5820919699648992</v>
+        <v>0.5165855041189171</v>
       </c>
       <c r="G16">
-        <v>-8.058107352533231</v>
+        <v>-5.095953694178325</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-15.94162230662175</v>
       </c>
       <c r="E17">
-        <v>-19.7142970494918</v>
+        <v>-16.94502651042519</v>
       </c>
       <c r="F17">
-        <v>1.193442852211588</v>
+        <v>0.956748464005268</v>
       </c>
       <c r="G17">
-        <v>-7.274517776115437</v>
+        <v>-5.596147330252348</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-16.58668102248056</v>
       </c>
       <c r="E18">
-        <v>-19.59808282103295</v>
+        <v>-18.45861913427492</v>
       </c>
       <c r="F18">
-        <v>1.824854307851872</v>
+        <v>1.133472365718515</v>
       </c>
       <c r="G18">
-        <v>-7.56525981701085</v>
+        <v>-5.279275153415467</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-17.23199870881199</v>
       </c>
       <c r="E19">
-        <v>-22.02909899409662</v>
+        <v>-17.98350975528618</v>
       </c>
       <c r="F19">
-        <v>1.697159815975522</v>
+        <v>1.719732827701809</v>
       </c>
       <c r="G19">
-        <v>-7.716859628890696</v>
+        <v>-5.46795307533515</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-17.82890384212984</v>
       </c>
       <c r="E20">
-        <v>-22.02428069775246</v>
+        <v>-19.17662227361308</v>
       </c>
       <c r="F20">
-        <v>1.821623674980954</v>
+        <v>2.053480397554924</v>
       </c>
       <c r="G20">
-        <v>-8.289852161373293</v>
+        <v>-5.835165407642189</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-18.33835254485047</v>
       </c>
       <c r="E21">
-        <v>-23.2820643533829</v>
+        <v>-20.81184065236083</v>
       </c>
       <c r="F21">
-        <v>2.059096728545905</v>
+        <v>2.27131617346911</v>
       </c>
       <c r="G21">
-        <v>-9.395951773681345</v>
+        <v>-5.559810782413308</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-18.72469853519074</v>
       </c>
       <c r="E22">
-        <v>-23.29177340165535</v>
+        <v>-20.00344011488155</v>
       </c>
       <c r="F22">
-        <v>2.26412594441281</v>
+        <v>2.941129085168373</v>
       </c>
       <c r="G22">
-        <v>-7.692897900277451</v>
+        <v>-6.077580104755322</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-18.970017019941</v>
       </c>
       <c r="E23">
-        <v>-23.73947192747566</v>
+        <v>-21.02575217906115</v>
       </c>
       <c r="F23">
-        <v>2.456535811265468</v>
+        <v>3.176831089226139</v>
       </c>
       <c r="G23">
-        <v>-8.089789273344056</v>
+        <v>-6.040392746712689</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-19.05776633704464</v>
       </c>
       <c r="E24">
-        <v>-22.86240161014408</v>
+        <v>-21.46212499138828</v>
       </c>
       <c r="F24">
-        <v>2.733811918534935</v>
+        <v>3.518968364134808</v>
       </c>
       <c r="G24">
-        <v>-8.687617518462265</v>
+        <v>-6.205555863666928</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-18.99339806353653</v>
       </c>
       <c r="E25">
-        <v>-24.61796871411967</v>
+        <v>-21.26097923291558</v>
       </c>
       <c r="F25">
-        <v>2.571291204310089</v>
+        <v>3.280917110122703</v>
       </c>
       <c r="G25">
-        <v>-8.362555051961227</v>
+        <v>-6.79401195436346</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-18.78194864875949</v>
       </c>
       <c r="E26">
-        <v>-23.2634613821594</v>
+        <v>-21.70936608678506</v>
       </c>
       <c r="F26">
-        <v>2.563804419723587</v>
+        <v>3.02002611008061</v>
       </c>
       <c r="G26">
-        <v>-8.071803079429195</v>
+        <v>-6.86832708062902</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-18.45277474186942</v>
       </c>
       <c r="E27">
-        <v>-24.12953656460036</v>
+        <v>-21.49780030962071</v>
       </c>
       <c r="F27">
-        <v>2.742368953805854</v>
+        <v>3.253372237244813</v>
       </c>
       <c r="G27">
-        <v>-7.959138593636719</v>
+        <v>-6.995713562434635</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-18.03079432438487</v>
       </c>
       <c r="E28">
-        <v>-23.71635406766651</v>
+        <v>-21.98376444080584</v>
       </c>
       <c r="F28">
-        <v>2.471688307797477</v>
+        <v>2.898451596576143</v>
       </c>
       <c r="G28">
-        <v>-9.303498168406119</v>
+        <v>-6.356947111177799</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-17.55856798224527</v>
       </c>
       <c r="E29">
-        <v>-24.29622516434869</v>
+        <v>-22.06966506425734</v>
       </c>
       <c r="F29">
-        <v>2.190853534165583</v>
+        <v>2.926089246603146</v>
       </c>
       <c r="G29">
-        <v>-8.998537334419536</v>
+        <v>-7.018400731015261</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-17.06793873150449</v>
       </c>
       <c r="E30">
-        <v>-22.99115518313016</v>
+        <v>-21.1046019684827</v>
       </c>
       <c r="F30">
-        <v>2.492195371221181</v>
+        <v>2.856713476618687</v>
       </c>
       <c r="G30">
-        <v>-8.452959429547645</v>
+        <v>-6.649301387750838</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-16.59768010181181</v>
       </c>
       <c r="E31">
-        <v>-23.57269275824717</v>
+        <v>-20.68905560811685</v>
       </c>
       <c r="F31">
-        <v>1.857551625975174</v>
+        <v>2.810705951067202</v>
       </c>
       <c r="G31">
-        <v>-7.254442627965297</v>
+        <v>-6.927916900335901</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-16.16921102012986</v>
       </c>
       <c r="E32">
-        <v>-23.38564413936035</v>
+        <v>-21.27565601717444</v>
       </c>
       <c r="F32">
-        <v>2.161867302006822</v>
+        <v>2.581185224569126</v>
       </c>
       <c r="G32">
-        <v>-7.872455269236442</v>
+        <v>-5.758095907487956</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-15.8051605259975</v>
       </c>
       <c r="E33">
-        <v>-21.55610894094347</v>
+        <v>-20.38696110706516</v>
       </c>
       <c r="F33">
-        <v>2.061962879759591</v>
+        <v>2.207392717729878</v>
       </c>
       <c r="G33">
-        <v>-7.433923854376884</v>
+        <v>-5.37538029042051</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-15.5084986689559</v>
       </c>
       <c r="E34">
-        <v>-22.39871304260268</v>
+        <v>-19.41534983787544</v>
       </c>
       <c r="F34">
-        <v>1.891358956418227</v>
+        <v>2.423611520473799</v>
       </c>
       <c r="G34">
-        <v>-7.571033408431339</v>
+        <v>-4.816798562670361</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-15.28307791690425</v>
       </c>
       <c r="E35">
-        <v>-22.58553523778912</v>
+        <v>-18.84907322016427</v>
       </c>
       <c r="F35">
-        <v>1.143528745988501</v>
+        <v>2.244342874099152</v>
       </c>
       <c r="G35">
-        <v>-7.333375965258139</v>
+        <v>-4.607197992942485</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-15.11439280092013</v>
       </c>
       <c r="E36">
-        <v>-21.87590071841714</v>
+        <v>-19.48420981363607</v>
       </c>
       <c r="F36">
-        <v>1.492069300920809</v>
+        <v>2.355564451803431</v>
       </c>
       <c r="G36">
-        <v>-6.296278053625115</v>
+        <v>-4.947538627107259</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-14.99405230589436</v>
       </c>
       <c r="E37">
-        <v>-21.65818527355037</v>
+        <v>-19.06040351668023</v>
       </c>
       <c r="F37">
-        <v>1.709833837238355</v>
+        <v>1.90746241872865</v>
       </c>
       <c r="G37">
-        <v>-6.817755186971113</v>
+        <v>-4.136296063799933</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-14.90063622201545</v>
       </c>
       <c r="E38">
-        <v>-21.93428633379803</v>
+        <v>-17.4791554911559</v>
       </c>
       <c r="F38">
-        <v>1.406479067393953</v>
+        <v>1.880523910789609</v>
       </c>
       <c r="G38">
-        <v>-6.396001616904582</v>
+        <v>-3.949448873563467</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-14.82530348959692</v>
       </c>
       <c r="E39">
-        <v>-21.25130641243519</v>
+        <v>-17.92127040852476</v>
       </c>
       <c r="F39">
-        <v>1.293653770397855</v>
+        <v>1.616062647241451</v>
       </c>
       <c r="G39">
-        <v>-6.146780438162708</v>
+        <v>-2.944294415838871</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-14.74908027190593</v>
       </c>
       <c r="E40">
-        <v>-21.21408688456615</v>
+        <v>-17.63180129300645</v>
       </c>
       <c r="F40">
-        <v>1.222730610104967</v>
+        <v>1.718289811686132</v>
       </c>
       <c r="G40">
-        <v>-5.089855669294988</v>
+        <v>-3.460137000677029</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-14.66962728858106</v>
       </c>
       <c r="E41">
-        <v>-20.78506831402748</v>
+        <v>-17.24334426415448</v>
       </c>
       <c r="F41">
-        <v>1.363162079166762</v>
+        <v>1.877644505697478</v>
       </c>
       <c r="G41">
-        <v>-5.397541082260392</v>
+        <v>-2.914582269623912</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-14.57618132995326</v>
       </c>
       <c r="E42">
-        <v>-20.3061006751842</v>
+        <v>-15.85072076647165</v>
       </c>
       <c r="F42">
-        <v>1.002744392413113</v>
+        <v>1.467756717648644</v>
       </c>
       <c r="G42">
-        <v>-4.934491767136992</v>
+        <v>-3.113052785248759</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-14.47663336855608</v>
       </c>
       <c r="E43">
-        <v>-20.03945506866455</v>
+        <v>-15.54100031519104</v>
       </c>
       <c r="F43">
-        <v>1.028712053756072</v>
+        <v>1.438077970341143</v>
       </c>
       <c r="G43">
-        <v>-5.026531554219809</v>
+        <v>-3.361479433061208</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-14.36895986813134</v>
       </c>
       <c r="E44">
-        <v>-19.60886511764522</v>
+        <v>-16.04559005996972</v>
       </c>
       <c r="F44">
-        <v>0.932326536235933</v>
+        <v>1.38603164642325</v>
       </c>
       <c r="G44">
-        <v>-4.869740806934386</v>
+        <v>-2.262490872571509</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-14.26824563491409</v>
       </c>
       <c r="E45">
-        <v>-19.76700395846707</v>
+        <v>-14.6030310794043</v>
       </c>
       <c r="F45">
-        <v>0.8470577092613631</v>
+        <v>1.288387010450856</v>
       </c>
       <c r="G45">
-        <v>-5.041074780773827</v>
+        <v>-2.460375421635905</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-14.17624263698009</v>
       </c>
       <c r="E46">
-        <v>-17.81248287743849</v>
+        <v>-13.84488301798815</v>
       </c>
       <c r="F46">
-        <v>0.4238820797042216</v>
+        <v>1.665550972619499</v>
       </c>
       <c r="G46">
-        <v>-5.692600074539015</v>
+        <v>-1.663215919052639</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-14.10890797122032</v>
       </c>
       <c r="E47">
-        <v>-16.52651852805832</v>
+        <v>-14.08323924738188</v>
       </c>
       <c r="F47">
-        <v>0.8425845252862457</v>
+        <v>1.184065733211897</v>
       </c>
       <c r="G47">
-        <v>-5.479986908370401</v>
+        <v>-2.71018587748377</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-14.06833094902262</v>
       </c>
       <c r="E48">
-        <v>-16.86139465245153</v>
+        <v>-13.58565052341906</v>
       </c>
       <c r="F48">
-        <v>1.070244738597634</v>
+        <v>1.013158627401109</v>
       </c>
       <c r="G48">
-        <v>-5.568381784814481</v>
+        <v>-2.128771317149268</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-14.06631075858006</v>
       </c>
       <c r="E49">
-        <v>-17.19274762406678</v>
+        <v>-13.27987890147314</v>
       </c>
       <c r="F49">
-        <v>0.6220979736831014</v>
+        <v>1.097304188177483</v>
       </c>
       <c r="G49">
-        <v>-6.110510101234452</v>
+        <v>-2.931492536238509</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-14.10383167809913</v>
       </c>
       <c r="E50">
-        <v>-16.29128694572988</v>
+        <v>-13.04469713235879</v>
       </c>
       <c r="F50">
-        <v>0.7788134891491286</v>
+        <v>1.216428390904468</v>
       </c>
       <c r="G50">
-        <v>-5.078371386819256</v>
+        <v>-2.762840104285878</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-14.18509935153829</v>
       </c>
       <c r="E51">
-        <v>-16.10550629956521</v>
+        <v>-12.38850766322533</v>
       </c>
       <c r="F51">
-        <v>0.8346437953630097</v>
+        <v>1.035406919105498</v>
       </c>
       <c r="G51">
-        <v>-5.376631676634354</v>
+        <v>-2.716787105289077</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-14.30830153687784</v>
       </c>
       <c r="E52">
-        <v>-15.49138635396301</v>
+        <v>-11.71796293148756</v>
       </c>
       <c r="F52">
-        <v>0.5930181360078247</v>
+        <v>0.4255562102252795</v>
       </c>
       <c r="G52">
-        <v>-5.582325802625891</v>
+        <v>-3.203814701753418</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-14.47056941254469</v>
       </c>
       <c r="E53">
-        <v>-15.65053957296258</v>
+        <v>-11.82934980665422</v>
       </c>
       <c r="F53">
-        <v>0.2806631543320067</v>
+        <v>0.5962222611218532</v>
       </c>
       <c r="G53">
-        <v>-4.880119367200002</v>
+        <v>-3.853688033294509</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-14.66912836647015</v>
       </c>
       <c r="E54">
-        <v>-15.18196931044091</v>
+        <v>-11.26285129371669</v>
       </c>
       <c r="F54">
-        <v>0.4253491183745796</v>
+        <v>0.6983665888262547</v>
       </c>
       <c r="G54">
-        <v>-6.345366822881429</v>
+        <v>-3.540814995469068</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-14.89535121473484</v>
       </c>
       <c r="E55">
-        <v>-14.68955663226886</v>
+        <v>-11.97905210039979</v>
       </c>
       <c r="F55">
-        <v>1.474304133600371</v>
+        <v>0.6615787924679286</v>
       </c>
       <c r="G55">
-        <v>-6.443193443566892</v>
+        <v>-4.224492307511657</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-15.14645529899328</v>
       </c>
       <c r="E56">
-        <v>-14.13832813368519</v>
+        <v>-11.12180291379978</v>
       </c>
       <c r="F56">
-        <v>0.2759679678929391</v>
+        <v>0.5682590627055503</v>
       </c>
       <c r="G56">
-        <v>-6.518726850590904</v>
+        <v>-4.02225108051758</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-15.40931736659812</v>
       </c>
       <c r="E57">
-        <v>-13.9231984474768</v>
+        <v>-11.24526270067089</v>
       </c>
       <c r="F57">
-        <v>0.1988328804464576</v>
+        <v>0.3105688743078745</v>
       </c>
       <c r="G57">
-        <v>-6.760284116409365</v>
+        <v>-4.433175856125155</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-15.68322397564108</v>
       </c>
       <c r="E58">
-        <v>-13.02848972388534</v>
+        <v>-10.41668328301344</v>
       </c>
       <c r="F58">
-        <v>0.8169034790646555</v>
+        <v>0.6219082775478603</v>
       </c>
       <c r="G58">
-        <v>-6.725076464599216</v>
+        <v>-4.095539937665966</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-15.95299566052458</v>
       </c>
       <c r="E59">
-        <v>-12.98335895192489</v>
+        <v>-10.47252389600203</v>
       </c>
       <c r="F59">
-        <v>-0.04890281687177657</v>
+        <v>0.596297642555508</v>
       </c>
       <c r="G59">
-        <v>-7.193710670047366</v>
+        <v>-4.755480638191981</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-16.22096660264147</v>
       </c>
       <c r="E60">
-        <v>-12.48332032352392</v>
+        <v>-10.07841080311447</v>
       </c>
       <c r="F60">
-        <v>-0.06513053429261888</v>
+        <v>0.5645794547023149</v>
       </c>
       <c r="G60">
-        <v>-7.767709608373901</v>
+        <v>-5.240929104434089</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-16.47196602081518</v>
       </c>
       <c r="E61">
-        <v>-12.78217696566013</v>
+        <v>-9.710916080444008</v>
       </c>
       <c r="F61">
-        <v>0.8537244101190935</v>
+        <v>0.5245303758791672</v>
       </c>
       <c r="G61">
-        <v>-7.373923527023133</v>
+        <v>-5.40445019080085</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-16.71028798720653</v>
       </c>
       <c r="E62">
-        <v>-13.19698518476273</v>
+        <v>-10.20954182495458</v>
       </c>
       <c r="F62">
-        <v>-0.0818461601137101</v>
+        <v>0.4703775136559551</v>
       </c>
       <c r="G62">
-        <v>-8.93824567905833</v>
+        <v>-5.057438807374445</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-16.92372785933646</v>
       </c>
       <c r="E63">
-        <v>-12.84196187950939</v>
+        <v>-9.304979141922431</v>
       </c>
       <c r="F63">
-        <v>-0.0538846184322128</v>
+        <v>0.6057493146214503</v>
       </c>
       <c r="G63">
-        <v>-8.087306364189603</v>
+        <v>-6.182663441262868</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-17.11775144636209</v>
       </c>
       <c r="E64">
-        <v>-13.09584624627542</v>
+        <v>-9.8299923044757</v>
       </c>
       <c r="F64">
-        <v>0.09214330080289526</v>
+        <v>0.2174057059846253</v>
       </c>
       <c r="G64">
-        <v>-7.357562810968055</v>
+        <v>-5.843365628942964</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-17.28285808018944</v>
       </c>
       <c r="E65">
-        <v>-12.92264117243005</v>
+        <v>-9.736017411868525</v>
       </c>
       <c r="F65">
-        <v>0.03589715415280882</v>
+        <v>0.4507137282483005</v>
       </c>
       <c r="G65">
-        <v>-9.283522336622157</v>
+        <v>-6.256131067870374</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-17.42436330782524</v>
       </c>
       <c r="E66">
-        <v>-11.90018872555621</v>
+        <v>-9.203278672658168</v>
       </c>
       <c r="F66">
-        <v>-0.01053449550890907</v>
+        <v>0.6302689897443157</v>
       </c>
       <c r="G66">
-        <v>-8.001364601990122</v>
+        <v>-5.684962645979916</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-17.53468631480955</v>
       </c>
       <c r="E67">
-        <v>-11.9270425764217</v>
+        <v>-9.805289478763859</v>
       </c>
       <c r="F67">
-        <v>0.01823470439031777</v>
+        <v>0.1566913455638383</v>
       </c>
       <c r="G67">
-        <v>-7.934061211176739</v>
+        <v>-6.482380371115245</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-17.61905884790819</v>
       </c>
       <c r="E68">
-        <v>-12.0643685507043</v>
+        <v>-9.624426755371513</v>
       </c>
       <c r="F68">
-        <v>0.3267551733585768</v>
+        <v>0.2135173493958844</v>
       </c>
       <c r="G68">
-        <v>-8.806231054588812</v>
+        <v>-6.348601225873296</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-17.67149352817461</v>
       </c>
       <c r="E69">
-        <v>-11.70056453435009</v>
+        <v>-8.747673431220463</v>
       </c>
       <c r="F69">
-        <v>0.3223391467342527</v>
+        <v>0.05696916414522265</v>
       </c>
       <c r="G69">
-        <v>-7.935742968310689</v>
+        <v>-6.071230478411</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-17.6987786099949</v>
       </c>
       <c r="E70">
-        <v>-11.71906787914543</v>
+        <v>-9.142225786086758</v>
       </c>
       <c r="F70">
-        <v>0.233297106239931</v>
+        <v>0.128077050368935</v>
       </c>
       <c r="G70">
-        <v>-8.698148363822686</v>
+        <v>-6.031964097769704</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-17.69735069431428</v>
       </c>
       <c r="E71">
-        <v>-12.36661701987225</v>
+        <v>-9.077740316217531</v>
       </c>
       <c r="F71">
-        <v>0.1581095105574311</v>
+        <v>-0.1465176316176703</v>
       </c>
       <c r="G71">
-        <v>-8.085624607055653</v>
+        <v>-6.349852612087141</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-17.67562010308447</v>
       </c>
       <c r="E72">
-        <v>-11.84142724683268</v>
+        <v>-9.308457009960321</v>
       </c>
       <c r="F72">
-        <v>-0.3596930125237063</v>
+        <v>0.2449447802906949</v>
       </c>
       <c r="G72">
-        <v>-8.386420774753834</v>
+        <v>-6.783649946825541</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-17.63097281608785</v>
       </c>
       <c r="E73">
-        <v>-12.38623436927348</v>
+        <v>-9.882019942349825</v>
       </c>
       <c r="F73">
-        <v>-0.4762434777301939</v>
+        <v>0.1442616926848317</v>
       </c>
       <c r="G73">
-        <v>-8.453224273190786</v>
+        <v>-6.110149251770672</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-17.57253944092825</v>
       </c>
       <c r="E74">
-        <v>-13.47260622676558</v>
+        <v>-9.71715178915257</v>
       </c>
       <c r="F74">
-        <v>-0.05393183537417236</v>
+        <v>0.1461636242416594</v>
       </c>
       <c r="G74">
-        <v>-7.578528483532249</v>
+        <v>-5.454694340450369</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-17.49765294093751</v>
       </c>
       <c r="E75">
-        <v>-12.64216560629098</v>
+        <v>-9.399031018587735</v>
       </c>
       <c r="F75">
-        <v>-0.06316150497616446</v>
+        <v>-0.02025124514374727</v>
       </c>
       <c r="G75">
-        <v>-8.205794099585658</v>
+        <v>-6.494553247063146</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-17.41702398035763</v>
       </c>
       <c r="E76">
-        <v>-13.8573136791392</v>
+        <v>-9.93128521107927</v>
       </c>
       <c r="F76">
-        <v>0.2595049941297018</v>
+        <v>-0.06147329220925907</v>
       </c>
       <c r="G76">
-        <v>-7.209531767179544</v>
+        <v>-5.94004680087184</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-17.3279488794703</v>
       </c>
       <c r="E77">
-        <v>-12.50567287122579</v>
+        <v>-11.73597267261606</v>
       </c>
       <c r="F77">
-        <v>0.2654394182033574</v>
+        <v>0.06192694305097769</v>
       </c>
       <c r="G77">
-        <v>-8.430739047888057</v>
+        <v>-6.592452699750473</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-17.24195600194289</v>
       </c>
       <c r="E78">
-        <v>-13.20224274308564</v>
+        <v>-11.31212561939415</v>
       </c>
       <c r="F78">
-        <v>-0.3516520501447315</v>
+        <v>-0.2677955895919347</v>
       </c>
       <c r="G78">
-        <v>-8.152395000037213</v>
+        <v>-5.705991231245367</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-17.1543676938041</v>
       </c>
       <c r="E79">
-        <v>-14.77567462247273</v>
+        <v>-11.6685708654859</v>
       </c>
       <c r="F79">
-        <v>-0.4147347129701222</v>
+        <v>0.07150369859474277</v>
       </c>
       <c r="G79">
-        <v>-7.605317418036032</v>
+        <v>-5.779349609850077</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-17.07629820729053</v>
       </c>
       <c r="E80">
-        <v>-15.16335728226939</v>
+        <v>-12.53358638500906</v>
       </c>
       <c r="F80">
-        <v>-0.3052949535492656</v>
+        <v>-0.1371231169025211</v>
       </c>
       <c r="G80">
-        <v>-8.592714109487977</v>
+        <v>-6.553911328582278</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-17.00109778107291</v>
       </c>
       <c r="E81">
-        <v>-14.33090601933538</v>
+        <v>-11.3241985310986</v>
       </c>
       <c r="F81">
-        <v>-0.585966538802808</v>
+        <v>-0.3163942483793761</v>
       </c>
       <c r="G81">
-        <v>-7.264483512585906</v>
+        <v>-5.128575809922304</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-16.93685349253623</v>
       </c>
       <c r="E82">
-        <v>-17.36542739492727</v>
+        <v>-12.45975414478801</v>
       </c>
       <c r="F82">
-        <v>-0.2913527017927471</v>
+        <v>-0.1328470843692701</v>
       </c>
       <c r="G82">
-        <v>-8.690603630538687</v>
+        <v>-5.965329437155254</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-16.87645642062145</v>
       </c>
       <c r="E83">
-        <v>-17.33062154370431</v>
+        <v>-14.26834515091941</v>
       </c>
       <c r="F83">
-        <v>-0.6038998647060145</v>
+        <v>-0.03686083993728016</v>
       </c>
       <c r="G83">
-        <v>-7.439790141072472</v>
+        <v>-5.164637582481585</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-16.82337515066324</v>
       </c>
       <c r="E84">
-        <v>-17.0824158833439</v>
+        <v>-14.28524541591604</v>
       </c>
       <c r="F84">
-        <v>-0.6057040489093118</v>
+        <v>-0.07788407882612007</v>
       </c>
       <c r="G84">
-        <v>-7.30403128959804</v>
+        <v>-6.080523179739734</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-16.77104416214526</v>
       </c>
       <c r="E85">
-        <v>-18.23397512417642</v>
+        <v>-15.81737761235317</v>
       </c>
       <c r="F85">
-        <v>-0.2970642950350497</v>
+        <v>-0.4310800585621621</v>
       </c>
       <c r="G85">
-        <v>-8.37898860001817</v>
+        <v>-5.350690241788626</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-16.7197927211369</v>
       </c>
       <c r="E86">
-        <v>-18.53648171636281</v>
+        <v>-17.16492015128965</v>
       </c>
       <c r="F86">
-        <v>-0.7914215355147526</v>
+        <v>-0.2116008017208219</v>
       </c>
       <c r="G86">
-        <v>-7.499105185499594</v>
+        <v>-5.343291172508355</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-16.6664812024876</v>
       </c>
       <c r="E87">
-        <v>-20.506716602198</v>
+        <v>-17.6487106149511</v>
       </c>
       <c r="F87">
-        <v>-0.07672353609479796</v>
+        <v>-0.4407694720727079</v>
       </c>
       <c r="G87">
-        <v>-6.880529751486773</v>
+        <v>-5.64778853011944</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-16.61093186744861</v>
       </c>
       <c r="E88">
-        <v>-22.54321211971343</v>
+        <v>-18.3468473388176</v>
       </c>
       <c r="F88">
-        <v>-0.6206950137977745</v>
+        <v>-0.27301678933178</v>
       </c>
       <c r="G88">
-        <v>-8.268519005918229</v>
+        <v>-6.200619840267874</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-16.5542017704368</v>
       </c>
       <c r="E89">
-        <v>-22.70812555765076</v>
+        <v>-20.00275631530639</v>
       </c>
       <c r="F89">
-        <v>-0.7832281535336627</v>
+        <v>-0.3546863599411861</v>
       </c>
       <c r="G89">
-        <v>-7.35285852575675</v>
+        <v>-5.937520854625376</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-16.49460362505733</v>
       </c>
       <c r="E90">
-        <v>-25.01930925152346</v>
+        <v>-22.31863603672504</v>
       </c>
       <c r="F90">
-        <v>-0.7281500049215236</v>
+        <v>-0.06747232894033309</v>
       </c>
       <c r="G90">
-        <v>-8.515462529329085</v>
+        <v>-5.528294388879447</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-16.43733724122445</v>
       </c>
       <c r="E91">
-        <v>-25.67881809210454</v>
+        <v>-22.96646594284034</v>
       </c>
       <c r="F91">
-        <v>-0.3261838943456607</v>
+        <v>-0.1592380414550595</v>
       </c>
       <c r="G91">
-        <v>-7.669022245848227</v>
+        <v>-6.33041308868054</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-16.38040016018529</v>
       </c>
       <c r="E92">
-        <v>-27.82368452109753</v>
+        <v>-25.89796453475773</v>
       </c>
       <c r="F92">
-        <v>-0.200023538899296</v>
+        <v>-0.1830975077578937</v>
       </c>
       <c r="G92">
-        <v>-8.052423145842303</v>
+        <v>-5.706126963612476</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-16.33477908500965</v>
       </c>
       <c r="E93">
-        <v>-29.82784220572418</v>
+        <v>-27.09024834234123</v>
       </c>
       <c r="F93">
-        <v>-0.4636572634120582</v>
+        <v>-0.1044200002073994</v>
       </c>
       <c r="G93">
-        <v>-7.838780400010975</v>
+        <v>-7.266195064629709</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-16.29873308444082</v>
       </c>
       <c r="E94">
-        <v>-31.95205652900519</v>
+        <v>-29.23743787850015</v>
       </c>
       <c r="F94">
-        <v>-0.4798394206257466</v>
+        <v>-0.1661963276385754</v>
       </c>
       <c r="G94">
-        <v>-8.643110544232304</v>
+        <v>-6.608813415805551</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-16.28542498397568</v>
       </c>
       <c r="E95">
-        <v>-32.90115675390278</v>
+        <v>-30.79600730619407</v>
       </c>
       <c r="F95">
-        <v>-0.3948000514217521</v>
+        <v>-0.1266757472184137</v>
       </c>
       <c r="G95">
-        <v>-7.726850855328216</v>
+        <v>-7.423727374115929</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-16.29342666900461</v>
       </c>
       <c r="E96">
-        <v>-35.74299835317931</v>
+        <v>-32.39187777428916</v>
       </c>
       <c r="F96">
-        <v>-0.4447191278492559</v>
+        <v>-0.2346327289882593</v>
       </c>
       <c r="G96">
-        <v>-9.553414561711241</v>
+        <v>-7.090239569217446</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-16.33010412448257</v>
       </c>
       <c r="E97">
-        <v>-39.31568810831676</v>
+        <v>-35.82507694456834</v>
       </c>
       <c r="F97">
-        <v>-0.1284269159079319</v>
+        <v>0.1050683173887759</v>
       </c>
       <c r="G97">
-        <v>-9.74483361533744</v>
+        <v>-6.973519665139362</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-16.3950934736784</v>
       </c>
       <c r="E98">
-        <v>-40.69139549134394</v>
+        <v>-38.43794078412103</v>
       </c>
       <c r="F98">
-        <v>-0.8267199272828452</v>
+        <v>0.07255075499188135</v>
       </c>
       <c r="G98">
-        <v>-8.061272234068774</v>
+        <v>-7.442763010966738</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-16.48762373858467</v>
       </c>
       <c r="E99">
-        <v>-42.98588949426136</v>
+        <v>-40.52732208533503</v>
       </c>
       <c r="F99">
-        <v>-0.01254577156290626</v>
+        <v>0.08649797695281662</v>
       </c>
       <c r="G99">
-        <v>-8.360234359538198</v>
+        <v>-7.579908981022125</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-16.61234380311618</v>
       </c>
       <c r="E100">
-        <v>-45.25796302236682</v>
+        <v>-42.0338525539698</v>
       </c>
       <c r="F100">
-        <v>-0.3844496007237723</v>
+        <v>0.3123523493261018</v>
       </c>
       <c r="G100">
-        <v>-9.362392773549754</v>
+        <v>-7.477891209683944</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-16.75435914346048</v>
       </c>
       <c r="E101">
-        <v>-45.92156786768783</v>
+        <v>-44.20042169464455</v>
       </c>
       <c r="F101">
-        <v>-0.7898642047974895</v>
+        <v>0.2911776217757409</v>
       </c>
       <c r="G101">
-        <v>-9.811928441781848</v>
+        <v>-7.503064597964562</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-16.93667441148822</v>
       </c>
       <c r="E102">
-        <v>-49.39487799648995</v>
+        <v>-46.11174113363995</v>
       </c>
       <c r="F102">
-        <v>-0.3128099026274627</v>
+        <v>0.410907361074173</v>
       </c>
       <c r="G102">
-        <v>-9.364104325593557</v>
+        <v>-7.555003746930188</v>
       </c>
     </row>
   </sheetData>
